--- a/output/2026-09-08_06_Croazia_Krapinsko-zagorska_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-08_06_Croazia_Krapinsko-zagorska_Utensilerie_e_Macchine_Utensili.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Import/ingrosso/dettaglio e assistenza utensili professionali multi-brand (Makita, Bosch, Milwaukee, DeWalt, Fein, Rems, Stanley, Stayer). Filiale di Zabok confermata da fonti terze; centralino sede legale Zagabria: 01 222 5690.</t>
+          <t>Import/ingrosso/dettaglio e assistenza utensili professionali multi-brand (Makita, Bosch, Milwaukee, DeWalt, Fein, Rems, Stanley, Stayer). Filiale di Zabok confermata da fonti terze; centralino sede legale Zagabria: 01 222 5690. [DUPLICATO — vedi anche: 2026-09-07_23_Croazia_Zagrebacka_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">

--- a/output/2026-09-08_06_Croazia_Krapinsko-zagorska_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-08_06_Croazia_Krapinsko-zagorska_Utensilerie_e_Macchine_Utensili.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
